--- a/Test upload format/Mudra/IA/2026 - 2027/cp6 25-26.xlsx
+++ b/Test upload format/Mudra/IA/2026 - 2027/cp6 25-26.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>custid</t>
   </si>
@@ -74,25 +74,55 @@
     <t>pan</t>
   </si>
   <si>
-    <t>MUSML0011</t>
+    <t>taruncategoryearlier</t>
+  </si>
+  <si>
+    <t>accountsrepaidsatisfactorily</t>
+  </si>
+  <si>
+    <t>AnyLoansInNPASuitFiledSettledOTS</t>
+  </si>
+  <si>
+    <t>modifiedloancat</t>
+  </si>
+  <si>
+    <t>HomeStay</t>
+  </si>
+  <si>
+    <t>2627CR701</t>
+  </si>
+  <si>
+    <t>10000</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>10-12-2026</t>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>01-04-2026</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t>30-12-2031</t>
-  </si>
-  <si>
-    <t>MUSML0012</t>
-  </si>
-  <si>
-    <t>01-01-2027</t>
+    <t>29-07-2031</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>2627CR702</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>2627CR710</t>
   </si>
 </sst>
 </file>
@@ -266,7 +296,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,121 +305,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -694,49 +730,49 @@
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -749,11 +785,14 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -763,12 +802,12 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1288,8 +1327,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:T4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="19.5714285714286" customWidth="1"/>
     <col min="2" max="2" width="23.4285714285714" customWidth="1"/>
@@ -1297,7 +1336,7 @@
     <col min="9" max="9" width="13.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:15">
+    <row r="1" s="1" customFormat="1" spans="1:20">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1343,87 +1382,151 @@
       <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:14">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="2">
-        <v>50000</v>
+    <row r="2" s="2" customFormat="1" spans="1:20">
+      <c r="A2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2">
-        <v>50000</v>
+        <v>22</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="2">
+        <v>25</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="8">
         <v>1</v>
       </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
+      <c r="K2" s="8">
         <v>1</v>
       </c>
-      <c r="M2" s="8">
-        <v>100000</v>
+      <c r="L2" s="8">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:14">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="2">
-        <v>50000</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2">
-        <v>50000</v>
+    <row r="3" customFormat="1" spans="1:20">
+      <c r="A3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3" s="8">
+        <v>1</v>
+      </c>
+      <c r="L3" s="8">
+        <v>1</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:20">
+      <c r="A4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="8">
         <v>1</v>
       </c>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="L4" s="8">
         <v>1</v>
       </c>
-      <c r="M3" s="8">
-        <v>100000</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>21</v>
+      <c r="M4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
